--- a/backend/data/golden_set/review/jd_manual_review_round2.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round2.xlsx
@@ -607,22 +607,34 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>["HTML5", "CSS3", "JavaScript", "DOM", "BOM", "AJAX", "跨域", "浏览器渲染机制", "事件机制", "Android原生", "iOS原生", "React Native", "Vue.js", "Vue Router", "Pinia", "Vuex", "Axios", "组件封装", "状态", "路由配置", "Vite", "Webpack", "Git", "ESLint", "Prettier", "响应式布局", "Flex", "Grid", "RESTful API", "表单校验", "权限控制", "性能调优"]</t>
+          <t>["HTML5","CSS3","JavaScript","Vue","React Native","Vue Router","Pinia","Vuex","Axios","Vite","Webpack","Git","ESLint","Prettier","RESTful API","Flex","Grid","Android开发","iOS开发"]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>["微信小程序开发","Uni-app","Taro","数据可视化","Jest","微前端","PWA","Web性能优化","Web安全"]</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>["后台管理系统开发：Web端、H5页面、微信小程序开发与迭代", "多端适配与兼容：PC端、移动端响应式布局，浏览器与手机机型适配", "移动端打包上架：微信小程序调试发布、安卓iOS打包、适配测试、上架提交"]</t>
+          <t>["Web/H5/微信小程序开发与多端适配","前端性能优化与兼容性排查","组件封装与代码规范制定","安卓/iOS 打包与上架"]</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>title 与草稿一致；skills 草稿 32→19（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -695,12 +707,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>["Go", "Python", "Linux", "Docker", "PostgreSQL", "MongoDB", "Redis", "微服务", "数据结构"]</t>
+          <t>["Golang","Python","Linux","Docker","PostgreSQL","MongoDB","Redis","微服务"]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["AI工具"]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>{"min_years":3,"max_years":5}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -710,12 +727,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>["微服务架构设计：技术选型、迭代和核心代码开发", "大数据中间件研发：大数据中间件产品研发", "系统维护与优化：维护和优化现有项目，确保系统稳定性和高效性"]</t>
+          <t>["业务后端开发与微服务架构设计","大数据中间件产品研发","技术文档编写与系统优化"]</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>草稿 skills 9→8（AI 工具属『附加项』移 bonus）；数据结构与算法为通用基础不单列；3-5 年经验</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -778,27 +805,43 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>大模型应用工程师</t>
+          <t>算法工程师</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>["Python", "Transformer", "检索增强生成", "Embedding", "向量数据库", "LangChain", "LlamaIndex", "FastAPI", "模型量化", "推理加速", "PyTorch", "Redis", "Apache Kafka", "Docker", "Kubernetes", "高并发"]</t>
+          <t>["Python","FastAPI","LangChain","LlamaIndex","RAG","Agent","Transformer","Qwen","DeepSeek","GLM","Milvus","Chroma","Elasticsearch","Redis","Kafka","PyTorch","vLLM","TGI","模型量化","Docker","Kubernetes"]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>["昇腾CANN","MindIE","VLM","OCR","CUDA","Triton"]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>{"min_years":3,"max_years":null}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>["RAG链路开发：文档切片策略优化、Embedding模型微调、向量数据库选型与调优、Hybrid Search实现", "Agent架构设计：Tool Calling、Function Calling、Multi-Agent协作、ReAct/Reflexion Prompt范式", "工程化接口开发：FastAPI开发RESTful API，高并发处理，SSE/WebSocket流式输出", "模型部署与优化：LLM/VLM模型量化、推理加速、服务化部署，昇腾/寒武纪国产硬件适配", "容器化交付：Docker和K8s弹性伸缩推理集群，KV Cache监控、显存管理及日志追踪"]</t>
+          <t>["RAG 链路全流程开发","Agent 架构设计与 Prompt 范式","FastAPI 高并发接口开发","模型量化与推理加速部署"]</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>⚠️ title 按 round1 先例归并（public_007/008 大模型算法工程师→算法工程师）；skills 21 项；无学历条款（仅年限）；3 年+</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -872,17 +915,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>物理设计工程师</t>
+          <t>数字后端工程师</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>["物理", "平面规划", "布局布线", "电源分析", "时序收敛", "物理验证", "时序分析", "Perl", "Tcl", "脚本语言", "数字后端"]</t>
+          <t>["布局布线","时序分析","物理验证","电源分析","Perl","TCL","Cadence","Innovus","ICC2","数字后端设计"]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["DDR设计","PCIE设计","PHY设计"]</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>{"min_years":7,"max_years":null}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -892,12 +940,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>["顶层/块级物理设计：从后DFT网表到GDS，完成实施与签核检查", "数字后端P&amp;R：placement/CTS/route，16nm及以下工艺tapeout经验", "关键模块P&amp;R：DDR/PCIE/PHY等特殊关键模块布局布线", "顶层STA/电源/物理验证：顶层时序分析、电源分析、物理验证"]</t>
+          <t>["顶层/块级物理设计（网表到 GDS）","时序收敛与物理验证","设计流程优化与客户技术沟通"]</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿『物理设计工程师』为职责描述，按标题为数字后端工程师；中英双语正文（中文为主）；7 年+；本科（机电工程硕士亦可）</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -962,17 +1020,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>图像识别算法工程师</t>
+          <t>图像算法工程师</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>["目标检测", "目标跟踪", "图像分割", "特征提取", "图像增强", "障碍物识别", "Python", "C++", "YOLO", "ByteTrack", "DeepSORT", "OpenCV", "PyTorch", "模型量化", "模型剪枝", "ONNX", "TensorRT", "NCNN", "计算机视觉", "深度学习"]</t>
+          <t>["目标检测","目标跟踪","图像分割","特征提取","图像增强","障碍物识别","YOLO","ByteTrack","DeepSORT","OpenCV","PyTorch","ONNX","TensorRT","NCNN","模型量化","Python","C/C++"]</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["SLAM","视觉定位","语义分割"]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>{"min_years":2,"max_years":4}</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -982,12 +1045,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>["无人机图像识别算法研发：目标检测、目标跟踪、图像分割、特征提取、图像增强、障碍物识别等核心算法研发，室内/室外场景", "算法嵌入式平台部署：配合嵌入式、飞控、硬件团队，完成算法在无人机嵌入式平台的部署与优化", "算法测试平台搭建：设计测试用例，开展算法性能测试、兼容性测试，分析测试数据，排查算法缺陷"]</t>
+          <t>["无人机场景图像识别算法研发与落地","算法实时性与鲁棒性优化","嵌入式平台部署与性能优化","算法测试平台搭建"]</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>title 保留细分（round1 无归并先例）；模型剪枝并入量化；2-4 年 CV 经验；本科</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1120,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>全栈开发工程师</t>
+          <t>Java开发工程师</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>["Java", "Spring Boot", "Spring Cloud", "HTML", "CSS", "JavaScript", "Vue.js", "React", "Element UI", "MySQL", "SQL", "Redis", "消息队列", "MES", "WMS", "ERP", "OPC UA", "Modbus", "PLM", "数据集成", "性能调优"]</t>
+          <t>["Java","Spring Boot","Spring Cloud","HTML","CSS","JavaScript","Vue","React","Element UI","MySQL","SQL"]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Redis","消息队列","MES","WMS","ERP","OPC UA","Modbus"]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{"min_years":3,"max_years":5}</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1067,12 +1145,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>["制造业数字化软件开发：MES、WMS生产管理系统后端核心功能开发与前端页面设计，支撑工厂生产流程数字化、智能化升级", "前后端交互与数据可视化：Java后端接口开发，配合前端实现数据可视化、生产看板等制造业特色功能", "第三方系统集成：对接ERP、PLM、自动化产线设备等第三方系统，完成接口开发与数据集成，解决跨系统数据流转问题", "系统高可用保障：代码编写、单元测试、性能优化及线上问题排查，保障系统高可用、高稳定性"]</t>
+          <t>["制造业数字化软件（MES/WMS）后端开发与前端实现","Java 接口开发与第三方系统数据集成","单元测试与性能优化"]</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿『全栈开发工程师』——职责含前端但岗位为 Java 开发，按标题 Java开发工程师；Redis/MQ『了解优先』入 bonus；3-5 年</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1145,27 +1233,39 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>数据分析师</t>
+          <t>数据分析工程师</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>["SQL", "Excel", "PPT", "数据清洗", "数据建模", "指标体系搭建", "统计学", "数据分析"]</t>
+          <t>["Excel","PPT","SQL","Python","Pandas","Numpy","数据可视化","数据分析","数据建模","数据清洗","数仓建模"]</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>["BI","数据挖掘","指标体系"]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>["数据需求调研与管理：承接业务端数据需求调研，梳理核心业务逻辑，明确数据口径、分析目标及输出标准", "数据质量管理：数据质量监控，数据缺失、异常、重复等问题治理", "数据分析与洞察：日常业务数据采集、整理、校验、统计、专项分析，输出数据洞察报告", "数据建模应用：搭建基础分析模型、趋势预测模型，参与数据仓库建模与底层数据建设", "数据报表与指标体系设计：核心数据报表、可视化看板设计开发维护，核心指标体系搭建"]</t>
+          <t>["数据需求调研与管理","数据质量监控与治理","业务数据分析与洞察报告","数仓建模与报表指标体系"]</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>⚠️ title：保留『数据分析工程师』（round1 数据分析师为另一岗位，未归一）；无学历/年限条款（实习优先非年限）</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1330,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>["检索增强生成", "大语言模型", "自然语言处理", "OCR", "PyTorch", "TensorFlow", "LangChain", "LlamaIndex", "Milvus", "pgvector", "提示工程", "LoRA", "QLoRA", "Python", "FastAPI", "Docker", "MySQL", "Redis", "向量检索", "重排序", "模型微调", "模型推理", "Agent开发"]</t>
+          <t>["大模型","RAG","NLP","OCR","OpenAI API","LangChain","LlamaIndex","Milvus","PGVector","PyTorch","TensorFlow","LoRA","QLoRA","Python","FastAPI","Docker","MySQL","Redis","Agent","Prompt工程","向量检索"]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["模型量化","显存优化","SFT微调","医药行业大模型"]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{"min_years":5,"max_years":null}</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1245,12 +1350,22 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>["企业级大模型文档智能应用开发：基于大模型搭建私有知识库、智能文档处理体系，实现OCR识别、文本解析、智能生成、精准检索、内容合规校验", "统一大模型服务中台搭建：模型接口封装、调用监控、成本管控、流量熔断与异常告警，满足企业内网私有化部署", "大模型平台迭代优化：搭建专属向量库、提示词模板库与业务语料库，优化向量检索精度、多轮对话体验与接口响应速度", "RAG知识库开发：文档切片、向量检索、重排序全流程，模型轻量化微调"]</t>
+          <t>["大模型文档智能应用开发与落地","RAG 知识库与私有化部署","模型服务中台建设","Prompt 优化与轻量化微调"]</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>title 与草稿一致；模型实例名（Qwen/DeepSeek/Llama/文心/通义）并入『大模型』不单列；5 年+；本科（硕士加分）</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1311,14 +1426,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>["大模型测试", "功能测试", "性能测试", "安全性测试", "自动化测试", "Python", "Java"]</t>
+          <t>["软件测试","自动化测试","Python","Java","大模型"]</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>["Transformer","Prompt工程","LLM测试"]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1326,12 +1442,22 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>["大模型全生命周期测试：功能测试、性能测试、安全性测试及多模态场景验证", "模型专项测试用例设计：针对模型推理逻辑、输出一致性、边界条件的专项测试", "自动化测试框架构建：提升大模型迭代过程中的测试效率与覆盖度", "测试数据分析与质量改进：分析测试数据与模型输出结果，支撑模型性能调优"]</t>
+          <t>["大模型全生命周期测试策略制定","专项测试用例设计与缺陷定位","自动化测试框架构建","测试数据分析与质量改进"]</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>⚠️ Transformer/Prompt/LLM 测试为『优先』条款→bonus（草稿误入 skills）；无年限；本科</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1395,19 +1521,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>机器人控制算法工程师</t>
+          <t>机器人算法工程师</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>["机器人运动学", "机器人动力学", "运动控制", "轨迹规划", "路径规划", "力控", "阻抗控制", "导纳控制", "C++", "Python", "Linux", "ROS", "X86", "ARM", "Twincat", "EtherCAT", "姿态控制", "人工智能"]</t>
+          <t>["运动控制","轨迹规划","路径规划","力控","阻抗控制","导纳控制","机器人运动学","机器人动力学","C/C++","Python","Linux","ROS"]</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>["TwinCAT","EtherCAT","医疗机器人","协作机器人","手术机器人"]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1415,12 +1542,22 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>["多关节机器人控制系统架构设计：运控、力控系统架构设计与算法开发", "运动控制与轨迹规划算法开发：运动控制、轨迹规划、路径规划算法开发", "力控功能开发：力/位混合控制、阻抗控制、导纳控制", "控制系统仿真与实机测试：仿真测试、实机测试、系统优化", "人工智能与机器人技术结合：基于人工智能的运动控制训练、遥操作"]</t>
+          <t>["多关节机器人运控/力控架构与算法开发","运动/轨迹/路径规划算法","力位混合与阻抗导纳控制","仿真与实机测试"]</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿『机器人控制算法工程师』按标题为机器人算法工程师；X86/ARM 硬件平台不单列；无年限</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1625,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>机器人系统工程师</t>
+          <t>SLAM算法工程师</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>["C++", "Python", "Linux", "ROS", "MAVROS", "Navigation2", "PCL", "OpenCV", "SLAM", "多传感器数据融合", "路径规划", "运动控制", "Jetson", "PX4", "DDS", "Git", "CI/CD"]</t>
+          <t>["SLAM","C++","Python","Linux","ROS","MAVROS","Navigation2","PCL","OpenCV","多传感器融合","卡尔曼滤波","路径规划","运动控制","Jetson","PX4","激光雷达"]</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1501,6 +1638,7 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1508,12 +1646,22 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>["ROS系统架构设计：节点划分与通信策略制定，基于DDS优化低延迟高可靠通信，适配室内巡检场景", "SLAM与定位导航：激光雷达+IMU融合SLAM，室内高精度定位，路径规划与动态避障", "飞控通信对接：基于MAVROS完成ROS与PX4飞控通信对接，姿态/位置控制与遥测回传", "传感器与硬件集成：激光雷达、IMU、相机等传感器ROS驱动开发，CAN/UART/Ethernet接口通信", "嵌入式计算平台适配：Jetson平台ROS系统裁剪、编译构建与量产级部署", "仿真环境搭建：Gazebo/Isaac Sim仿真环境，算法验证与性能测试", "自动化测试：rostest/gtest自动化测试用例，性能指标制定与测试报告"]</t>
+          <t>["ROS 系统架构与 SLAM 功能包开发","激光雷达+IMU 融合建图与定位","路径规划与动态避障","MAVROS 飞控对接与嵌入式部署"]</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿『机器人系统工程师』过泛，按标题为 SLAM算法工程师；A*/RRT* 并入路径规划；无年限</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1722,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>计算机视觉工程师</t>
+          <t>计算机视觉算法工程师</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>["Python", "C++", "Java", "OpenCV", "CNN", "Transformer", "预训练模型", "CLIP", "SAM", "扩散模型", "GAN", "图像生成", "模型训练", "模型调优", "模型部署", "模型轻量化", "图像分类", "目标检测", "图像分割"]</t>
+          <t>["Python","C/C++","Java","OpenCV","图像分类","目标检测","图像分割","CNN","Transformer","CLIP","SAM","大语言模型","扩散模型","GAN","模型轻量化"]</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1587,19 +1735,30 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>本科</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{"min_years":3,"max_years":null}</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>["视觉模型训练与调优：选择智能模型，训练调优以满足任务目标", "模型轻量化与部署：配合运行环境完成模型轻量化并部署", "模型持续更新：收集运行数据，持续更新模型", "算法开发与演示系统：配合算法开发，研发演示系统，支撑指标测试"]</t>
+          <t>["计算机视觉智能模型选型与训练调优","模型轻量化与部署","运行数据收集与模型迭代"]</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿少『算法』二字，按标题保留；无学历条款（仅专业要求）；3 年+</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1816,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>机器视觉算法工程师</t>
+          <t>摄影测量高级算法工程师</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>["多视几何", "摄影测量", "特征提取", "特征匹配", "光束平差法", "三维重建", "畸变校准", "传感器融合", "C++", "Python", "多线程", "OpenCV", "OpenMVS", "性能调优", "深度学习", "PyTorch", "CNN", "Transformer"]</t>
+          <t>["多视几何","摄影测量","三维重建","SFM","密集匹配","光束平差","特征提取与匹配","畸变校正","多传感器融合","相机标定","LiDAR","C++","Python","OpenCV","OpenMVS","GPU加速","PyTorch","CNN","Transformer"]</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1670,6 +1829,7 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1677,12 +1837,22 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>["多视几何与三维重建：特征提取与匹配、光束平差法、三维重建、畸变校准", "多传感器融合：相机与 LiDAR 联合标定、多模态数据配准", "AI 影像解译：基于 CNN 的影像解译，优化数据处理流程"]</t>
+          <t>["多视几何与摄影测量算法实现","多传感器融合与联合标定","AI 与传统方法结合优化处理流程"]</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿『机器视觉算法工程师』按标题为摄影测量高级算法工程师（级别保留）；SIFT/SURF/ORB 并入特征提取与匹配；无年限；本科（硕士优先）</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1912,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>前端开发工程师</t>
+          <t>React前端开发工程师</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>["React", "HTML5", "CSS3", "JavaScript", "Webpack", "Babel", "前端性能"]</t>
+          <t>["React","HTML5","CSS3","JavaScript","Webpack","Babel","前端性能优化"]</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1755,6 +1925,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{"min_years":3,"max_years":null}</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1762,12 +1937,22 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>["前端开发与实现：使用React及相关技术栈进行高质量前端开发", "跨平台适配：保证应用在各种浏览器、移动设备上的兼容性", "性能体验优化：页面加载优化、首屏渲染优化，确保流畅用户体验", "前后端协作开发：与后端团队紧密合作，确保接口正确对接"]</t>
+          <t>["React 前端开发与跨平台适配","性能与体验优化","前后端接口对接与代码维护"]</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿丢『React』前缀，按标题保留；3 年+；本科</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1832,27 +2017,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>前端开发工程师</t>
+          <t>高级前端工程师</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>["Android", "Vue.js", "uni-app", "HTML5", "CSS3", "JavaScript", "小程序"]</t>
+          <t>["Android开发","Vue","uni-app","HTML5","CSS3","JavaScript"]</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
+          <t>["iOS开发","微信小程序开发","混合开发","UI设计"]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>["前端架构设计：参与产品前端架构设计、性能优化及组件化开发", "页面实现与接口联调：根据产品需求独立完成页面实现、交互逻辑及接口联调"]</t>
+          <t>["移动端与 Web 前端开发维护","前端架构设计与组件化开发","页面实现与接口联调"]</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>⚠️ title：草稿去『高级』，按标题保留级别；skills 6 项；无学历/年限条款</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -1927,12 +2124,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>["JavaScript", "Java", "Vue.js", "Spring Boot", "Spring Cloud", "MySQL", "PostgreSQL", "SQL", "Redis", "MongoDB", "缓存", "消息队列", "RabbitMQ", "Apache Kafka", "RocketMQ", "Maven", "Gradle", "Git", "Linux", "系统设计", "性能调优"]</t>
+          <t>["JavaScript","Java","Vue","Spring Boot","Spring Cloud","MySQL","PostgreSQL","Redis","MongoDB","RabbitMQ","Kafka","RocketMQ","Maven","Gradle","Git","Linux","SQL"]</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Dubbo","gRPC","微服务","Docker","Kubernetes","分布式事务","分库分表","阿里云","腾讯云","AWS"]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{"min_years":1,"max_years":null}</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1942,12 +2144,22 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>["核心产品需求分析与系统设计：参与需求分析、系统设计、编码实现与模块测试", "高可用高性能系统开发：确保系统高可用、高性能和高扩展性", "系统架构规划与性能优化：解决技术难点和性能瓶颈"]</t>
+          <t>["核心产品需求分析与系统设计","全栈编码实现与模块测试","系统架构讨论与性能优化"]</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>title 与草稿一致；skills 17 项；1 年+；本科</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2221,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>客户端开发工程师</t>
+          <t>AI全栈工程师</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>["大语言模型", "VLM", "Python", "Java", "Go", "检索增强生成", "AGENT", "CI/CD", "性能监控", "UI设计", "组件化UI"]</t>
+          <t>["LLM","VLM","客户端开发","RAG","Agent","知识库构建","Python","Java","Go","CI/CD","UI设计","Figma"]</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2022,14 +2234,26 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>["端侧AI模型工程化落地：LLM/VLM模型端上部署及前后处理逻辑开发，实现低延时高并发AI服务", "客户端CI/CD流程建设：自动化构建、测试与多渠道打包发布", "客户端性能监控与稳定性治理：内存、卡顿监控，提升多终端用户体验", "多端UI设计与实现：大屏/多端界面高还原度实现，建立组件化UI库", "AI智能体云端服务开发：RAG架构、知识库构建、Agent框架后端工程化落地", "服务端部署与运维：部署、监控、日志分析与故障排查，保障高可用"]</t>
+          <t>["AI 智能体客户端开发与端侧 LLM/VLM 落地","客户端 CI/CD 与稳定性治理","UI/UX 设计实现","RAG/Agent 后端工程化"]</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>⚠️ title 修正：草稿『客户端开发工程师』按标题为 AI全栈工程师（职责为客户端+UI+后端三方向）；正文无任职要求节，skills 按职责推导，学历/年限留空</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -2101,17 +2325,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>计算金融软件工程师</t>
+          <t>Python工程师</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>["Python", "多线程", "并发编程", "异步编程", "MySQL", "PostgreSQL", "Git", "高性能计算", "并行计算", "性能调优"]</t>
+          <t>["Python","高性能计算","并行计算","多线程","并发编程","异步编程","MySQL","PostgreSQL","Git"]</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["AWS","GCP","Azure","Django","Flask","FastAPI","单元测试"]</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{"min_years":2,"max_years":null}</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2121,12 +2350,22 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>["计算金融应用开发：开发计算金融应用，关注性能、可扩展性和准确性", "高性能并行计算优化：实现高性能和并行计算方案，优化计算密集型任务", "金融模型集成：与精算团队协作，将金融模型和模拟集成到可扩展软件系统", "性能分析与调优：性能分析、剖析和优化，提升系统吞吐量和延迟"]</t>
+          <t>["计算金融应用开发","高性能并行计算优化","金融模型与仿真集成","API 与库实现"]</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>⚠️ title：草稿『计算金融软件工程师』为正文语义，按招聘标题为 Python工程师（英文 JD）；2 年+；本科/硕士</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2428,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Java 后端开发工程师</t>
+          <t>Java后端工程师</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>["Java", "计算机网络", "数据结构", "操作系统", "数据库", "Spring Boot", "Dubbo", "Thrift", "RPC", "ORM", "Redis", "本地缓存", "分布式缓存", "RabbitMQ", "Apache Kafka", "RocketMQ", "消息队列", "Web 容器", "达梦数据库", "SQL", "性能调优", "RESTful API"]</t>
+          <t>["Java","Spring Boot","Dubbo","Thrift","Redis","RabbitMQ","Kafka","RocketMQ","达梦数据库","SQL","存储过程","ORM","RESTful API"]</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2202,6 +2441,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{"min_years":1,"max_years":2}</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>本科</t>
@@ -2209,12 +2453,22 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>["后端功能开发：信息化产品后端功能开发、接口设计与版本迭代", "数据库设计：数据库设计、SQL 编写、存储过程开发，数据层方案落地", "接口联调：配合前端开展接口联调，定位并解决业务问题", "系统优化：优化信息化系统，保障系统稳定运行"]</t>
+          <t>["信息化产品后端开发与接口设计","数据库设计与 SQL 优化","接口联调与系统优化"]</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>⚠️ title：草稿加『开发』二字，按标题为 Java后端工程师（大小写规范）；1-2 年；本科；前端基础『优先』过泛不入 bonus</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -2301,17 +2555,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>机器视觉算法工程师</t>
+          <t>视觉算法工程师</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>["OpenCV", "C++", "Python", "深度学习", "视频动作检测", "目标检测", "目标跟踪", "目标分割", "人脸识别", "表情分析", "人体姿态估计", "OCR", "多模态模型", "少样本学习", "度量学习", "迁移学习", "自监督学习", "模型部署", "模型量化", "Linux", "多线程", "内存", "缓存"]</t>
+          <t>["目标检测","目标跟踪","图像分割","人脸识别","表情分析","人体姿态估计","OCR","视频动作检测","视频行为理解","多模态大模型","少样本学习","度量学习","迁移学习","自监督学习","OpenCV","C/C++","Python","Linux","ONNX","RKNN","模型量化","嵌入式部署"]</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["TensorRT","NCNN","MNN","OpenVINO","LLM","VLM","强化学习","ISP"]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2321,12 +2580,22 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>["仿生机器人视觉算法研发：视频与图像理解，覆盖动作检测、目标检测跟踪、分割、人脸识别、表情分析、姿态估计、OCR", "嵌入式部署与性能优化：视觉算法在机器人本体上的迁移、裁剪、部署、验证与性能优化", "图像处理链路设计：相机采集后图像格式转换、畸变校正、增强、ROI、检测结果输出", "算法工程化：算法接口封装、服务调用、内存管理、缓存优化和多线程调度"]</t>
+          <t>["仿生机器人视觉算法研发","多模态大模型算法设计与落地","嵌入式部署与性能优化","图像处理链路设计"]</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>AI预标_待复核</t>
+          <t>AI已复核_待终审</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>⚠️ title：草稿『机器视觉算法工程师』，正文自述亦为机器视觉——按招聘标题为视觉算法工程师（终审可改）；22 项 skills；3 年+；硕士</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>

--- a/backend/data/golden_set/review/jd_manual_review_round2.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round2.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>算法工程师</t>
+          <t>大模型应用工程师</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>⚠️ title 按 round1 先例归并（public_007/008 大模型算法工程师→算法工程师）；skills 21 项；无学历条款（仅年限）；3 年+</t>
+          <t>title 按正文判断（终审口径）：正文为 LLM 工程化落地与 Agent 应用（RAG/部署为主，非算法研究）→ 大模型应用工程师，不做 round1『大模型算法→算法工程师』归并；skills 21 项；无学历条款（仅年限）；3 年+</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>["布局布线","时序分析","物理验证","电源分析","Perl","TCL","Cadence","Innovus","ICC2","数字后端设计"]</t>
+          <t>["物理设计","布局布线","时序分析","物理验证","电源分析","Perl","TCL","Cadence","Innovus","ICC2","数字后端设计"]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>⚠️ title 修正：草稿『物理设计工程师』为职责描述，按标题为数字后端工程师；中英双语正文（中文为主）；7 年+；本科（机电工程硕士亦可）</t>
+          <t>title 按标题为数字后端工程师（芯片物理设计岗，终审确认保留芯片物理设计语义）；skills 补『物理设计』（正文任职条件『熟悉亚微米物理设计方法』）；中英双语正文（中文为主）；7 年+；本科（机电工程硕士亦可）</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>摄影测量高级算法工程师</t>
+          <t>摄影测量算法工程师</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>⚠️ title 修正：草稿『机器视觉算法工程师』按标题为摄影测量高级算法工程师（级别保留）；SIFT/SURF/ORB 并入特征提取与匹配；无年限；本科（硕士优先）</t>
+          <t>title 按标题为摄影测量算法工程师（终审口径：级别不保留，去『高级』）；SIFT/SURF/ORB 并入特征提取与匹配；无年限；本科（硕士优先）</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>高级前端工程师</t>
+          <t>前端工程师</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>⚠️ title：草稿去『高级』，按标题保留级别；skills 6 项；无学历/年限条款</t>
+          <t>title 按标题去级别（终审口径：级别不保留）→ 前端工程师；skills 6 项；无学历/年限条款</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">

--- a/backend/data/golden_set/review/jd_manual_review_round2.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round2.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>title 与草稿一致；skills 草稿 32→19（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款</t>
+          <t>title 与草稿一致；skills 草稿 32→19（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款；双框架（Vue 全家桶 + React Native）无主导方向，保留『前端开发工程师』（终审细化口径下不可单一框架前缀，否则失真）</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>草稿 skills 9→8（AI 工具属『附加项』移 bonus）；数据结构与算法为通用基础不单列；3-5 年经验</t>
+          <t>草稿 skills 9→8（AI 工具属『附加项』移 bonus）；数据结构与算法为通用基础不单列；3-5 年经验；语言为 Golang 或 Python 二选一、无主导语言，保留『后端开发工程师』（终审细化口径下不可单语言前缀，否则失真）</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>React前端开发工程师</t>
+          <t>React前端工程师</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>⚠️ title 修正：草稿丢『React』前缀，按标题保留；3 年+；本科</t>
+          <t>title 保留 React 细化（终审口径：移除泛化『前端工程师』，保留『React前端工程师』格式）；3 年+；本科</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>前端工程师</t>
+          <t>Vue前端工程师</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>title 按标题去级别（终审口径：级别不保留）→ 前端工程师；skills 6 项；无学历/年限条款</t>
+          <t>title 按终审口径细化：移除泛化『前端工程师』，主框架 Vue/uniapp → Vue前端工程师；skills 6 项；无学历/年限条款</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">

--- a/backend/data/golden_set/review/jd_manual_review_round2.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round2.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>前端开发工程师</t>
+          <t>React前端工程师</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>title 与草稿一致；skills 草稿 32→19（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款；双框架（Vue 全家桶 + React Native）无主导方向，保留『前端开发工程师』（终审细化口径下不可单一框架前缀，否则失真）</t>
+          <t>title 按终审口径细分（移除泛词『前端开发工程师』）：双栈（RN+Vue+小程序+原生）取硬性必备 React Native（『无原生+RN 开发经验者不考虑』），格式对齐 r2_014『React前端工程师』；skills 19 项（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>后端开发工程师</t>
+          <t>Golang后端工程师</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>草稿 skills 9→8（AI 工具属『附加项』移 bonus）；数据结构与算法为通用基础不单列；3-5 年经验；语言为 Golang 或 Python 二选一、无主导语言，保留『后端开发工程师』（终审细化口径下不可单语言前缀，否则失真）</t>
+          <t>title 按终审口径细分（移除泛词『后端开发工程师』）：『熟练掌握 Golang 或 Python』二选一取序首 Golang，格式对齐 r2_019『Java后端工程师』；skills 8 项（AI 工具属『附加项』移 bonus；数据结构与算法为通用基础不单列）；3-5 年经验</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">

--- a/backend/data/golden_set/review/jd_manual_review_round2.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round2.xlsx
@@ -615,8 +615,6 @@
           <t>["微信小程序开发","Uni-app","Taro","数据可视化","Jest","微前端","PWA","Web性能优化","Web安全"]</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>["Web/H5/微信小程序开发与多端适配","前端性能优化与兼容性排查","组件封装与代码规范制定","安卓/iOS 打包与上架"]</t>
@@ -624,7 +622,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -634,7 +632,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -732,7 +730,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -742,7 +740,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -823,7 +821,6 @@
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>["RAG 链路全流程开发","Agent 架构设计与 Prompt 范式","FastAPI 高并发接口开发","模型量化与推理加速部署"]</t>
@@ -831,7 +828,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -841,7 +838,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -945,7 +942,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -955,7 +952,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1047,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1060,7 +1057,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1147,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1160,7 +1157,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1246,8 +1243,6 @@
           <t>["BI","数据挖掘","指标体系"]</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>["数据需求调研与管理","数据质量监控与治理","业务数据分析与洞察报告","数仓建模与报表指标体系"]</t>
@@ -1255,7 +1250,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1265,7 +1260,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1350,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1365,7 +1360,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1429,6 @@
           <t>["Transformer","Prompt工程","LLM测试"]</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1447,7 +1441,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1457,7 +1451,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1528,6 @@
           <t>["TwinCAT","EtherCAT","医疗机器人","协作机器人","手术机器人"]</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1547,7 +1540,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1557,7 +1550,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1631,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1651,7 +1643,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1661,7 +1653,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1732,6 @@
           <t>{"min_years":3,"max_years":null}</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>["计算机视觉智能模型选型与训练调优","模型轻量化与部署","运行数据收集与模型迭代"]</t>
@@ -1748,7 +1739,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1758,7 +1749,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1820,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>本科</t>
@@ -1842,7 +1832,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1852,7 +1842,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1932,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1952,7 +1942,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2030,8 +2020,6 @@
           <t>["iOS开发","微信小程序开发","混合开发","UI设计"]</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>["移动端与 Web 前端开发维护","前端架构设计与组件化开发","页面实现与接口联调"]</t>
@@ -2039,7 +2027,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2049,7 +2037,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2137,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2159,7 +2147,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2234,8 +2222,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>["AI 智能体客户端开发与端侧 LLM/VLM 落地","客户端 CI/CD 与稳定性治理","UI/UX 设计实现","RAG/Agent 后端工程化"]</t>
@@ -2243,7 +2229,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2253,7 +2239,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2341,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2365,7 +2351,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2444,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2468,7 +2454,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2541,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>视觉算法工程师</t>
+          <t>机器视觉算法工程师</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2585,7 +2571,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>AI已复核_待终审</t>
+          <t>人工终审_定稿</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2595,7 +2581,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ZKT</t>
         </is>
       </c>
     </row>

--- a/backend/data/golden_set/review/jd_manual_review_round2.xlsx
+++ b/backend/data/golden_set/review/jd_manual_review_round2.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>React前端工程师</t>
+          <t>前端开发工程师</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>title 按终审口径细分（移除泛词『前端开发工程师』）：双栈（RN+Vue+小程序+原生）取硬性必备 React Native（『无原生+RN 开发经验者不考虑』），格式对齐 r2_014『React前端工程师』；skills 19 项（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款</t>
+          <t>title 按终审口径细分（移除泛词『前端开发工程师』）：双栈（RN+Vue+小程序+原生）取硬性必备 React Native（『无原生+RN 开发经验者不考虑』），格式对齐 r2_014『React前端工程师』；skills 19 项（DOM/BOM/AJAX 等 JS 子能力不单列，对齐 round1 粒度）；无学历/年限条款 | 口径修订 08-14：标题无细分词不保留正文细分（标题含细分词才保留，对齐 r2_014）</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Vue前端工程师</t>
+          <t>前端工程师</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>title 按终审口径细化：移除泛化『前端工程师』，主框架 Vue/uniapp → Vue前端工程师；skills 6 项；无学历/年限条款</t>
+          <t>title 按终审口径细化：移除泛化『前端工程师』，主框架 Vue/uniapp → Vue前端工程师；skills 6 项；无学历/年限条款 | 口径修订 08-14：标题无细分词不保留正文细分（标题含细分词才保留，对齐 r2_014）</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
